--- a/Config/Excel/LevelConfig.xlsx
+++ b/Config/Excel/LevelConfig.xlsx
@@ -1195,7 +1195,7 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>11001</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1234,9 +1234,6 @@
       <c r="H6">
         <v>3</v>
       </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
@@ -1260,9 +1257,6 @@
       <c r="H7">
         <v>3</v>
       </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
@@ -1314,9 +1308,6 @@
       <c r="H10">
         <v>3</v>
       </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
@@ -1340,9 +1331,6 @@
       <c r="H11">
         <v>3</v>
       </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
@@ -1366,9 +1354,6 @@
       <c r="H12">
         <v>3</v>
       </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
@@ -1404,7 +1389,7 @@
         <v>4</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>11002</v>
       </c>
     </row>
   </sheetData>
